--- a/results_per_subdiv.xlsx
+++ b/results_per_subdiv.xlsx
@@ -512,10 +512,10 @@
         <v>176</v>
       </c>
       <c r="E7">
-        <v>345.9083333333332</v>
+        <v>349.2416666666667</v>
       </c>
       <c r="F7">
-        <v>276.7266666666666</v>
+        <v>279.3933333333334</v>
       </c>
     </row>
     <row r="8">
@@ -534,10 +534,10 @@
         <v>362</v>
       </c>
       <c r="E8">
-        <v>159.9166666666667</v>
+        <v>160.75</v>
       </c>
       <c r="F8">
-        <v>127.9333333333333</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="9">
@@ -798,10 +798,10 @@
         <v>123</v>
       </c>
       <c r="E20">
-        <v>74.47056277056275</v>
+        <v>75.62348484848485</v>
       </c>
       <c r="F20">
-        <v>59.5764502164502</v>
+        <v>60.49878787878788</v>
       </c>
     </row>
     <row r="21">
